--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_ARB_Ax3.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_ARB_Ax3.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6165E9CD-BF01-4A53-AABA-7CDF6D104D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC832A7-271D-40C7-A5CE-E53C0A861DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29985" yWindow="0" windowWidth="26085" windowHeight="15585" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="27285" windowHeight="11295" tabRatio="988" activeTab="7" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
-    <sheet name="BuARB_Sedan_f" sheetId="51" r:id="rId1"/>
-    <sheet name="BuARB_Sedan_r" sheetId="53" r:id="rId2"/>
-    <sheet name="BuARB_SedanLG_f" sheetId="54" r:id="rId3"/>
-    <sheet name="BuARB_SedanLG_r" sheetId="55" r:id="rId4"/>
-    <sheet name="BuARB_SedanLG_mac_f" sheetId="57" r:id="rId5"/>
-    <sheet name="BuARB_Ach_f" sheetId="50" r:id="rId6"/>
-    <sheet name="BuARB_Makhulu_f" sheetId="52" r:id="rId7"/>
-    <sheet name="BuARB_SedanLGAU_f" sheetId="49" r:id="rId8"/>
+    <sheet name="Sef_DW" sheetId="51" r:id="rId1"/>
+    <sheet name="Ser_DW" sheetId="53" r:id="rId2"/>
+    <sheet name="SLGf_S2LAR" sheetId="54" r:id="rId3"/>
+    <sheet name="SLGr_DW" sheetId="55" r:id="rId4"/>
+    <sheet name="SLGf_MacP" sheetId="57" r:id="rId5"/>
+    <sheet name="Achf_DW" sheetId="50" r:id="rId6"/>
+    <sheet name="Makf_DW" sheetId="52" r:id="rId7"/>
+    <sheet name="SLGf_S2LAF" sheetId="49" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="44">
   <si>
     <t>Units</t>
   </si>
@@ -141,46 +141,40 @@
     <t>sAxialOrientationX</t>
   </si>
   <si>
-    <t>sMount</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_SedanLG_f</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_Sedan_f</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_Ach_f</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_Makhulu_f</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_Sedan_r</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_SedanLGAU_f</t>
-  </si>
-  <si>
-    <t>AntiRollBar.Droplink_Sedan_Hamba_r.sInboard</t>
-  </si>
-  <si>
-    <t>AntiRollBar.Droplink_Sedan_Hamba_f.sInboard</t>
-  </si>
-  <si>
-    <t>AntiRollBar.Droplink_Sedan_HambaLG_r.sInboard</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_SedanLG_r</t>
-  </si>
-  <si>
-    <t>BushARB_Ax3_SedanLG_mac_f</t>
-  </si>
-  <si>
     <t>AxisAttachment</t>
   </si>
   <si>
     <t>Outer</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_Ser_DW</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_SLGf_S2LAR</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_SLGr_DW</t>
+  </si>
+  <si>
+    <t>AntiRollBar.sMount</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_SLGf_MacP</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_Achf_DW</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_Makf_DW</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_SLGf_S2LAF</t>
+  </si>
+  <si>
+    <t>Sedan_HambaLG_Upr_f</t>
+  </si>
+  <si>
+    <t>BushARB_Ax3_Sef_DW</t>
   </si>
 </sst>
 </file>
@@ -769,10 +763,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -790,7 +784,7 @@
       </c>
       <c r="G5" s="20">
         <f>K5+0.01</f>
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H5" s="20">
         <f>L5</f>
@@ -800,7 +794,7 @@
         <v>-0.3</v>
       </c>
       <c r="K5" s="21">
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="L5" s="21">
         <v>0.15</v>
@@ -821,7 +815,7 @@
       </c>
       <c r="G6" s="20">
         <f>K5</f>
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="20">
         <f>L5</f>
@@ -830,7 +824,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -841,7 +835,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1742,10 +1736,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1763,7 +1757,7 @@
       </c>
       <c r="G5" s="20">
         <f>K5+0.01</f>
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H5" s="20">
         <f>L5</f>
@@ -1773,7 +1767,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" s="21">
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="L5" s="21">
         <v>0.15</v>
@@ -1794,7 +1788,7 @@
       </c>
       <c r="G6" s="20">
         <f>K5</f>
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="20">
         <f>L5</f>
@@ -1803,7 +1797,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -1814,7 +1808,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -2715,11 +2709,13 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>32</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -2776,7 +2772,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -2787,7 +2783,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -3689,10 +3685,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>41</v>
+        <v>36</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -3750,7 +3746,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -3761,7 +3757,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4663,10 +4659,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -4724,7 +4720,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -4735,7 +4731,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -5638,7 +5634,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -5698,7 +5697,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -5709,7 +5708,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="S7" s="4"/>
     </row>
@@ -6614,7 +6613,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -6632,7 +6634,7 @@
       </c>
       <c r="G5" s="20">
         <f>K5+0.01</f>
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H5" s="20">
         <f>L5</f>
@@ -6642,7 +6644,7 @@
         <v>-0.3</v>
       </c>
       <c r="K5" s="21">
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="L5" s="21">
         <v>0.3</v>
@@ -6663,7 +6665,7 @@
       </c>
       <c r="G6" s="20">
         <f>K5</f>
-        <v>0.57999999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="20">
         <f>L5</f>
@@ -6672,7 +6674,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -6683,7 +6685,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -7573,6 +7575,9 @@
       <c r="H3" s="19" t="s">
         <v>29</v>
       </c>
+      <c r="J3" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
@@ -7583,10 +7588,10 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>41</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -7644,7 +7649,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>19</v>
@@ -7655,7 +7660,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="18"/>
       <c r="H7" s="19" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
